--- a/CDcontrol_Python/wavelength_calibration.xlsx
+++ b/CDcontrol_Python/wavelength_calibration.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desde\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lguser\Desktop\Des\CD\CDcontrol_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC35505-23CD-436B-BB57-B9B44A91B63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0118F9F1-274B-41CF-8D1A-B29D3CED1179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wavelength Calibration" sheetId="1" r:id="rId1"/>
@@ -205,6 +205,9 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -243,9 +246,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -371,7 +371,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1139,7 +1139,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1312,40 +1312,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>348</c:v>
+                  <c:v>1786</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>465</c:v>
+                  <c:v>1708</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>567</c:v>
+                  <c:v>1631</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>643</c:v>
+                  <c:v>1504</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>910</c:v>
+                  <c:v>1338</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>967</c:v>
+                  <c:v>1248</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>971</c:v>
+                  <c:v>1153</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1186</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1306</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1392</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1570</c:v>
+                  <c:v>608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1357,40 +1351,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>253.7</c:v>
+                  <c:v>650</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>313.2</c:v>
+                  <c:v>627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>365</c:v>
+                  <c:v>604</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>404.7</c:v>
+                  <c:v>568</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>435.8</c:v>
+                  <c:v>545</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>546.1</c:v>
+                  <c:v>520</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>577</c:v>
+                  <c:v>495</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>579.1</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>696.5</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>763.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>811.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>912.3</c:v>
+                  <c:v>320</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1493,40 +1481,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>348</c:v>
+                  <c:v>1786</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>465</c:v>
+                  <c:v>1708</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>567</c:v>
+                  <c:v>1631</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>643</c:v>
+                  <c:v>1504</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>910</c:v>
+                  <c:v>1338</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>967</c:v>
+                  <c:v>1248</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>971</c:v>
+                  <c:v>1153</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1186</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1306</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1392</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1570</c:v>
+                  <c:v>608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1538,40 +1520,40 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>253.81293395756239</c:v>
+                  <c:v>649.96286502231158</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>312.88200466473074</c:v>
+                  <c:v>626.92469714219919</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>365.18213296559122</c:v>
+                  <c:v>604.37576545196771</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>404.61694970064468</c:v>
+                  <c:v>567.58861726307009</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>436.0207115321482</c:v>
+                  <c:v>544.94835170796046</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>546.10038647810507</c:v>
+                  <c:v>520.22132243874262</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>576.85959026523358</c:v>
+                  <c:v>494.85933684582454</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>579.02504433965544</c:v>
+                  <c:v>468.31746888737894</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>696.68449573958389</c:v>
+                  <c:v>439.79276961898074</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>763.36491489377624</c:v>
+                  <c:v>320.00880562156465</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>811.55874973639027</c:v>
+                  <c:v>160.48594554922158</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>912.29208572657831</c:v>
+                  <c:v>160.48594554922158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1907,7 +1889,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2324,40 +2306,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>348</c:v>
+                  <c:v>1786</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>465</c:v>
+                  <c:v>1708</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>567</c:v>
+                  <c:v>1631</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>643</c:v>
+                  <c:v>1504</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>910</c:v>
+                  <c:v>1338</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>967</c:v>
+                  <c:v>1248</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>971</c:v>
+                  <c:v>1153</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1186</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1306</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1392</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1570</c:v>
+                  <c:v>608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2369,40 +2345,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>253.7</c:v>
+                  <c:v>650</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>313.2</c:v>
+                  <c:v>627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>365</c:v>
+                  <c:v>604</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>404.7</c:v>
+                  <c:v>568</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>435.8</c:v>
+                  <c:v>545</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>546.1</c:v>
+                  <c:v>520</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>577</c:v>
+                  <c:v>495</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>579.1</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>696.5</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>763.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>811.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>912.3</c:v>
+                  <c:v>320</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2497,40 +2467,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>348</c:v>
+                  <c:v>1786</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>465</c:v>
+                  <c:v>1708</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>567</c:v>
+                  <c:v>1631</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>643</c:v>
+                  <c:v>1504</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>910</c:v>
+                  <c:v>1338</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>967</c:v>
+                  <c:v>1248</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>971</c:v>
+                  <c:v>1153</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1186</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1306</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1392</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1570</c:v>
+                  <c:v>608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2542,40 +2506,40 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>253.81293395756239</c:v>
+                  <c:v>649.96286502231158</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>312.88200466473074</c:v>
+                  <c:v>626.92469714219919</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>365.18213296559122</c:v>
+                  <c:v>604.37576545196771</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>404.61694970064468</c:v>
+                  <c:v>567.58861726307009</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>436.0207115321482</c:v>
+                  <c:v>544.94835170796046</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>546.10038647810507</c:v>
+                  <c:v>520.22132243874262</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>576.85959026523358</c:v>
+                  <c:v>494.85933684582454</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>579.02504433965544</c:v>
+                  <c:v>468.31746888737894</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>696.68449573958389</c:v>
+                  <c:v>439.79276961898074</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>763.36491489377624</c:v>
+                  <c:v>320.00880562156465</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>811.55874973639027</c:v>
+                  <c:v>160.48594554922158</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>912.29208572657831</c:v>
+                  <c:v>160.48594554922158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4649,16 +4613,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>933450</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>43543</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>81644</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>648315</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>18300</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76741</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>61843</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4704,9 +4668,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9C18372-B583-42F4-8F4E-BE2AF50AAC7B}" name="CalibData3" displayName="CalibData3" ref="L4:N16" totalsRowShown="0">
   <autoFilter ref="L4:N16" xr:uid="{D9C18372-B583-42F4-8F4E-BE2AF50AAC7B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{10163724-6C7E-460B-BFF8-B4C78224821D}" name="Pixel Number (X)" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{90881FAE-4CA8-4278-A028-53B6A49AAC38}" name="Wavelength [nm] (Y)" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{78A89D84-58C0-415B-B8F1-DA850D4314FA}" name="Fitted Wavelength [nm]" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{10163724-6C7E-460B-BFF8-B4C78224821D}" name="Pixel Number (X)" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{90881FAE-4CA8-4278-A028-53B6A49AAC38}" name="Wavelength [nm] (Y)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{78A89D84-58C0-415B-B8F1-DA850D4314FA}" name="Fitted Wavelength [nm]" dataDxfId="0">
       <calculatedColumnFormula>$P$5*L5^3 + $P$6*L5^2 + $P$7*L5 + $P$8</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4894,27 +4858,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:U16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" ht="42" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -4934,7 +4898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>348</v>
       </c>
@@ -4953,24 +4917,24 @@
         <v>-5.2175232839925515E-9</v>
       </c>
       <c r="L5" s="4">
-        <v>348</v>
+        <v>1786</v>
       </c>
       <c r="M5" s="4">
-        <v>253.7</v>
+        <v>650</v>
       </c>
       <c r="N5" s="5">
         <f t="shared" ref="N5:N16" ca="1" si="1">$P$5*L5^3 + $P$6*L5^2 + $P$7*L5 + $P$8</f>
-        <v>253.81293395756239</v>
+        <v>649.96286502231158</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="P5" s="7" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">INDEX(LINEST(OFFSET($M$5,0,0,COUNT($M$5:$M$4997),1),OFFSET($L$5,0,0,COUNT($L$5:$L$4997),1)^{1,2,3}),1,1)</f>
-        <v>-5.2175232839925515E-9</v>
+        <v>2.3143760517708634E-9</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>465</v>
       </c>
@@ -4989,24 +4953,24 @@
         <v>4.3193349678799193E-5</v>
       </c>
       <c r="L6" s="4">
-        <v>465</v>
+        <v>1708</v>
       </c>
       <c r="M6" s="4">
-        <v>313.2</v>
+        <v>627</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>312.88200466473074</v>
+        <v>626.92469714219919</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="P6" s="7" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">INDEX(LINEST(OFFSET($M$5,0,0,COUNT($M$5:$M$4997),1),OFFSET($L$5,0,0,COUNT($L$5:$L$4997),1)^{1,2,3}),1,2)</f>
-        <v>4.3193349678799193E-5</v>
+        <v>4.3830676624330535E-6</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>567</v>
       </c>
@@ -5025,24 +4989,24 @@
         <v>0.4723519804388378</v>
       </c>
       <c r="L7" s="4">
-        <v>567</v>
+        <v>1631</v>
       </c>
       <c r="M7" s="4">
-        <v>365</v>
+        <v>604</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>365.18213296559122</v>
+        <v>604.37576545196771</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="P7" s="7" cm="1">
         <f t="array" aca="1" ref="P7" ca="1">INDEX(LINEST(OFFSET($M$5,0,0,COUNT($M$5:$M$4997),1),OFFSET($L$5,0,0,COUNT($L$5:$L$4997),1)^{1,2,3}),1,3)</f>
-        <v>0.4723519804388378</v>
+        <v>0.25885267847142424</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>643</v>
       </c>
@@ -5061,24 +5025,24 @@
         <v>84.423445648390597</v>
       </c>
       <c r="L8" s="4">
-        <v>643</v>
+        <v>1504</v>
       </c>
       <c r="M8" s="4">
-        <v>404.7</v>
+        <v>568</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>404.61694970064468</v>
+        <v>567.58861726307009</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="P8" s="7" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">INDEX(LINEST(OFFSET($M$5,0,0,COUNT($M$5:$M$4997),1),OFFSET($L$5,0,0,COUNT($L$5:$L$4997),1)^{1,2,3}),1,4)</f>
-        <v>84.423445648390597</v>
+        <v>160.48594554922158</v>
       </c>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>703</v>
       </c>
@@ -5097,14 +5061,14 @@
         <v>0.99999940906255913</v>
       </c>
       <c r="L9" s="4">
-        <v>703</v>
+        <v>1425</v>
       </c>
       <c r="M9" s="4">
-        <v>435.8</v>
+        <v>545</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>436.0207115321482</v>
+        <v>544.94835170796046</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>7</v>
@@ -5114,7 +5078,7 @@
         <v>0.99999940906255913</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>910</v>
       </c>
@@ -5126,17 +5090,17 @@
         <v>546.10038647810507</v>
       </c>
       <c r="L10" s="4">
-        <v>910</v>
+        <v>1338</v>
       </c>
       <c r="M10" s="4">
-        <v>546.1</v>
+        <v>520</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>546.10038647810507</v>
+        <v>520.22132243874262</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>967</v>
       </c>
@@ -5155,14 +5119,14 @@
         <v>12</v>
       </c>
       <c r="L11" s="4">
-        <v>967</v>
+        <v>1248</v>
       </c>
       <c r="M11" s="4">
-        <v>577</v>
+        <v>495</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>576.85959026523358</v>
+        <v>494.85933684582454</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>8</v>
@@ -5171,7 +5135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>971</v>
       </c>
@@ -5183,17 +5147,17 @@
         <v>579.02504433965544</v>
       </c>
       <c r="L12" s="4">
-        <v>971</v>
+        <v>1153</v>
       </c>
       <c r="M12" s="4">
-        <v>579.1</v>
+        <v>468</v>
       </c>
       <c r="N12" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>579.02504433965544</v>
+        <v>468.31746888737894</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>1186</v>
       </c>
@@ -5206,18 +5170,18 @@
       </c>
       <c r="E13" s="9"/>
       <c r="L13" s="4">
-        <v>1186</v>
+        <v>1050</v>
       </c>
       <c r="M13" s="4">
-        <v>696.5</v>
+        <v>440</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>696.68449573958389</v>
+        <v>439.79276961898074</v>
       </c>
       <c r="O13" s="9"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>1306</v>
       </c>
@@ -5236,14 +5200,14 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="4">
-        <v>1306</v>
+        <v>608</v>
       </c>
       <c r="M14" s="4">
-        <v>763.5</v>
+        <v>320</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>763.36491489377624</v>
+        <v>320.00880562156465</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -5253,7 +5217,7 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>1392</v>
       </c>
@@ -5271,15 +5235,11 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="4">
-        <v>1392</v>
-      </c>
-      <c r="M15" s="4">
-        <v>811.5</v>
-      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
       <c r="N15" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>811.55874973639027</v>
+        <v>160.48594554922158</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -5289,7 +5249,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>1570</v>
       </c>
@@ -5300,15 +5260,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>912.29208572657831</v>
       </c>
-      <c r="L16" s="4">
-        <v>1570</v>
-      </c>
-      <c r="M16" s="4">
-        <v>912.3</v>
-      </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
       <c r="N16" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>912.29208572657831</v>
+        <v>160.48594554922158</v>
       </c>
     </row>
   </sheetData>
